--- a/templates/Handcraft-Setup-Example.xlsx
+++ b/templates/Handcraft-Setup-Example.xlsx
@@ -1184,7 +1184,7 @@
     <row r="5" ht="64" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>L8870_U</t>
+          <t>L8870-U</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
